--- a/Geopolitical_Ranking_20260615_1707.xlsx
+++ b/Geopolitical_Ranking_20260615_1707.xlsx
@@ -1,37 +1,311 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Programming\Projects\Country Ranking\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12030"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+  <si>
+    <t>Dim_Energy</t>
+  </si>
+  <si>
+    <t>Dim_Openness</t>
+  </si>
+  <si>
+    <t>Dim_Cohesion</t>
+  </si>
+  <si>
+    <t>Dim_Demography</t>
+  </si>
+  <si>
+    <t>Score_OSCI</t>
+  </si>
+  <si>
+    <t>HP_Pop</t>
+  </si>
+  <si>
+    <t>HP_GDP</t>
+  </si>
+  <si>
+    <t>HP_Military_Asym</t>
+  </si>
+  <si>
+    <t>HP_Geo</t>
+  </si>
+  <si>
+    <t>HP_EnergySecurity</t>
+  </si>
+  <si>
+    <t>Score_HardPower</t>
+  </si>
+  <si>
+    <t>FINAL_SCORE_1_10</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>RUS</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>ISR</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
+    <t>NLD</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>SWE</t>
+  </si>
+  <si>
+    <t>POL</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>IRQ</t>
+  </si>
+  <si>
+    <t>UZB</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>SAU</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>EGY</t>
+  </si>
+  <si>
+    <t>DNK</t>
+  </si>
+  <si>
+    <t>UKR</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>PAK</t>
+  </si>
+  <si>
+    <t>SVK</t>
+  </si>
+  <si>
+    <t>ETH</t>
+  </si>
+  <si>
+    <t>NGA</t>
+  </si>
+  <si>
+    <t>ROU</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>BGD</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>IRN</t>
+  </si>
+  <si>
+    <t>IRL</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>THA</t>
+  </si>
+  <si>
+    <t>CIV</t>
+  </si>
+  <si>
+    <t>PRT</t>
+  </si>
+  <si>
+    <t>SRB</t>
+  </si>
+  <si>
+    <t>HRV</t>
+  </si>
+  <si>
+    <t>NZL</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>HUN</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>GHA</t>
+  </si>
+  <si>
+    <t>VEN</t>
+  </si>
+  <si>
+    <t>PHL</t>
+  </si>
+  <si>
+    <t>KEN</t>
+  </si>
+  <si>
+    <t>SGP</t>
+  </si>
+  <si>
+    <t>QAT</t>
+  </si>
+  <si>
+    <t>LKA</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>MYS</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>OMN</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>ARE</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>BGR</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>LTU</t>
+  </si>
+  <si>
+    <t>JOR</t>
+  </si>
+  <si>
+    <t>KWT</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t>CHL</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>GTM</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>ZAF</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +320,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,3341 +644,3164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Dim_Energy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dim_Openness</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Dim_Cohesion</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dim_Demography</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Score_OSCI</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>HP_Pop</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>HP_GDP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>HP_Military_Asym</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>HP_Geo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>HP_EnergySecurity</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Score_HardPower</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>FINAL_SCORE_1_10</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
         <v>5.13</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>7.62</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>7.09</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>5.62</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>6.28</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>8.48</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>5.03</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>8.26</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>1.54</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>7.18</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>6.6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
         <v>8.07</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>4.07</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>4.34</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>4.92</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>5.15</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>8.67</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>7.78</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>8.51</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>6.67</v>
       </c>
-      <c r="L3" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="L3">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="M3">
         <v>6.34</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
         <v>6.39</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>6.38</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>5.55</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>4.49</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>5.65</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>7.53</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>7.66</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>6.4</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>8.58</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>8.1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>7.55</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>6.31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DEU</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
         <v>7.85</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>5.93</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>6.06</v>
       </c>
-      <c r="E5" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F5">
         <v>5.92</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>6.82</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>8.73</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>6.23</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>6.19</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>6.56</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>7</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>6.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>GBR</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
         <v>6.92</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6.42</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6.23</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>4.76</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>6.03</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>6.57</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>8.4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>6.26</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>6.03</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>6.11</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>6.79</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>6.3</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
         <v>8</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>5.6</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>5.3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>7.5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>6.49</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>4.01</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>5.71</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>2.71</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>6.09</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>5.88</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>6.28</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
         <v>7.56</v>
       </c>
-      <c r="C8" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="D8">
         <v>5.76</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>3.64</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>5.31</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>5.81</v>
       </c>
-      <c r="J8" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J8">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="K8">
         <v>3.91</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>8.02</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>6.26</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
         <v>6.61</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>6.42</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>6.3</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>4.88</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>6.01</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>6.56</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>8.18</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>5.83</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>6.58</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>5.56</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>6.69</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>6.25</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>KAZ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
         <v>5.72</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>6.5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6.56</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>7.74</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>6.59</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>4.97</v>
       </c>
-      <c r="H10" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="H10">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="I10">
         <v>4.66</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>6.38</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>7.46</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>5.39</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>6.17</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
         <v>6.84</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>7.9</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>7.28</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>4.51</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>6.49</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>4.79</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>6.84</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>5.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>4.29</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>4.76</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>5.45</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>6.13</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="C12">
         <v>5.5</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>5.98</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>3.93</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>5.78</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>7.34</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>8.52</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>5.9</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>6.27</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>3.43</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>6.67</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>6.09</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
         <v>6.43</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>6.59</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>6.28</v>
       </c>
-      <c r="E13" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F13">
         <v>5.76</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>5.89</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>7.7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>5.27</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>7.94</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>6.88</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>6.69</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>6.09</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>SWE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
         <v>6.93</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>7.53</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>6.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>4.51</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>6.3</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>4.09</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>5.87</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>6.55</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>5.72</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>6.06</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>5.67</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>6.08</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
         <v>6.37</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>7.29</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>6.85</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>3.91</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>5.94</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>5.73</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>6.45</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>6.36</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>5.91</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>6.65</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>6.19</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>6.03</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="C16" t="n">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="C16">
         <v>6.42</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>6.23</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>3.09</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>5.81</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>6.18</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>7.45</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>8.01</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>5.12</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>2.79</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>6.41</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>6.02</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>NOR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
         <v>6.63</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>7.82</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>7.16</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>4.55</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>6.41</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>3.25</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>5.56</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>5.67</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>5.55</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>6.87</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>5.25</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>6.01</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
         <v>6.69</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>7.58</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>7.08</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>4.53</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>6.35</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>4.24</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>6.02</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>5.75</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>4.26</v>
       </c>
-      <c r="K18" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K18">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="L18">
         <v>5.13</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>5.92</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>IRQ</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
         <v>4.12</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>6.75</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>6.23</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>8.23</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>6.15</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>6.03</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>4.79</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>4.67</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>5.4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>8.26</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>5.48</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>5.91</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>UZB</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C20" t="n">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C20">
         <v>6.75</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>6.16</v>
       </c>
-      <c r="E20" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="E20">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="F20">
         <v>6.5</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>5.72</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>3.55</v>
       </c>
-      <c r="I20" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J20" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="I20">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J20">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="K20">
         <v>5.87</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>4.78</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>5.9</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
         <v>6.3</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>7.86</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>7.27</v>
       </c>
-      <c r="E21" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E21">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F21">
         <v>6.3</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>4.13</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>5.09</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>5.58</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>4.74</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>7.1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>5.15</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>5.9</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
         <v>7.03</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>7.45</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>7</v>
       </c>
-      <c r="E22" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="E22">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F22">
         <v>6.24</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>3.26</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>4.88</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>6.53</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>5.5</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>5.39</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>5.14</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>5.86</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>SAU</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
         <v>5.68</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>5.5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>5.91</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>6.34</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>5.85</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>5.68</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>6.87</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>5.87</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>4.22</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>7.06</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>5.87</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>5.86</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24">
         <v>6.61</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>5.5</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>5.92</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>4.62</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>5.61</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>5.34</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>7.36</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>5.57</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>7.18</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>5.42</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>6.28</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>5.85</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EGY</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
         <v>4.84</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>6.59</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>6.43</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>7.22</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>6.2</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>7.25</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>5.25</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>4.82</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>3.85</v>
       </c>
-      <c r="K25" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K25">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="L25">
         <v>5.18</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>5.85</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>DNK</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
         <v>7.23</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>6.22</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>6.64</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>4.59</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>6.08</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>3.34</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>5.38</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>6.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>4.42</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>6.8</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>5.22</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>5.78</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>UKR</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
         <v>5.14</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>7.78</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>6.97</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>3.59</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>5.63</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>5.77</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>4.26</v>
       </c>
-      <c r="I27" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="I27">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="J27">
         <v>6.37</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>5.58</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>6.06</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>5.78</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
         <v>6.16</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>6.09</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>6.01</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>3.99</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>5.48</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>6.36</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>7.78</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>5.23</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>6.18</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>5.56</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>6.32</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>5.77</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>IDN</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
         <v>4.57</v>
       </c>
-      <c r="C29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="C29">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D29">
         <v>6.02</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>5.93</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>5.32</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>8.43</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>7.04</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>4.7</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>7.49</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>4.57</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>6.57</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>5.76</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>AUT</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30">
         <v>7.39</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>6.5</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>6.44</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>4.26</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>6.03</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>3.9</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>5.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>5.51</v>
       </c>
-      <c r="J30" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="K30" t="n">
+      <c r="J30">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="K30">
         <v>6.67</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>5.25</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>5.76</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>PAK</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="C31" t="n">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="C31">
         <v>5.31</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>5.73</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>8.91</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>5.82</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>8.27</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>5.19</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>4.76</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>6.33</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>1.54</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>5.56</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>5.73</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>SVK</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32">
         <v>5.35</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>8.98</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>7.52</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>4.57</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>6.38</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>3.21</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>3.83</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>5.19</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>4.45</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>6.53</v>
       </c>
-      <c r="L32" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="L32">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="M32">
         <v>5.7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
         <v>3.09</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>6.5</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>6.04</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>9.66</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>5.85</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>7.42</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>3.92</v>
       </c>
-      <c r="I33" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="I33">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J33">
         <v>6.38</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>4.97</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>5.4</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33">
         <v>5.69</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="C34" t="n">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="C34">
         <v>5.89</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>4.47</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>10</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>5.82</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>8.17</v>
       </c>
-      <c r="H34" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="H34">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="I34">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J34">
         <v>6.95</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34">
         <v>5.44</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34">
         <v>5.69</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>ROU</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
         <v>5.05</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>7.74</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>6.62</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>4.43</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>5.82</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>4.87</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>5.23</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>4.96</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>5.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>6.51</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35">
         <v>5.31</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35">
         <v>5.64</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>ESP</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36">
         <v>5.29</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>6.63</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>6.13</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>3.82</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>5.35</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>6.11</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>7.34</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>5.21</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>6.2</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>5.41</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>6.14</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36">
         <v>5.63</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>BGD</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37">
         <v>3.62</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>6.22</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>6.07</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>5.98</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>5.35</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>7.78</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>5.46</v>
       </c>
-      <c r="I37" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="I37">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J37">
         <v>6.01</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>8.26</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37">
         <v>6.11</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37">
         <v>5.61</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>CHE</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38">
         <v>7.31</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>5.76</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>6.08</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>4.22</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>5.73</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>3.88</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>6.48</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>5.26</v>
       </c>
-      <c r="J38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K38" t="n">
+      <c r="J38">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K38">
         <v>7.58</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38">
         <v>5.35</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38">
         <v>5.6</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>DZA</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39">
         <v>4.04</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>5.5</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>5.89</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>7.2</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>5.54</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>6.05</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>4.74</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>5.58</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>5.14</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>8.26</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39">
         <v>5.65</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39">
         <v>5.58</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>IRN</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40">
         <v>5.65</v>
       </c>
-      <c r="C40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="C40">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D40">
         <v>5.32</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>5.04</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>5.27</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>6.94</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>5.53</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>5.03</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>6.38</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40">
         <v>7.84</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40">
         <v>6.09</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40">
         <v>5.56</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>IRL</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41">
         <v>5.64</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>6.79</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>6.79</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>4.59</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>5.88</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>3.2</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>5.88</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>4.74</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41">
         <v>4.51</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>6.93</v>
       </c>
-      <c r="L41" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="L41">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="M41">
         <v>5.53</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42">
         <v>5.21</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>5.15</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>5.29</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>5.48</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>5.28</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>7.07</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>5.54</v>
       </c>
-      <c r="I42" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J42" t="n">
+      <c r="I42">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J42">
         <v>6.42</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>6.58</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42">
         <v>5.9</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42">
         <v>5.5</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43">
         <v>5.55</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>6.01</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>5.71</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>4.04</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>5.27</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>6.61</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>5.68</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>4.91</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>6.6</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>4.66</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43">
         <v>5.75</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43">
         <v>5.44</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44">
         <v>4.12</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>5.27</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>5.41</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>10</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>5.86</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>5.55</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>3.16</v>
       </c>
-      <c r="I44" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="I44">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="J44">
         <v>5.69</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44">
         <v>2.54</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44">
         <v>4.45</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44">
         <v>5.37</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>PRT</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45">
         <v>5.92</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>5.64</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>6.05</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>4.47</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>5.48</v>
       </c>
-      <c r="G45" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="G45">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H45">
         <v>4.95</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>5.33</v>
       </c>
-      <c r="J45" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="J45">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="K45">
         <v>5.97</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45">
         <v>4.93</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45">
         <v>5.29</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>SRB</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="C46" t="n">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="C46">
         <v>6.55</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>6.15</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>4.95</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>5.65</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>3.47</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>3.21</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>5.29</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>4.59</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K46">
         <v>8.26</v>
       </c>
-      <c r="L46" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="L46">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="M46">
         <v>5.27</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>HRV</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47">
         <v>5.46</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>7.12</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>6.63</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>4.57</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>5.86</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>2.76</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>3.25</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>5.3</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>4.7</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>4.95</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47">
         <v>4.13</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47">
         <v>5.25</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48">
         <v>6.07</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>5.5</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>5.85</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>4.8</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>5.53</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>3.18</v>
       </c>
-      <c r="H48" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="H48">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="I48">
         <v>5.13</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>5.31</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48">
         <v>5.42</v>
       </c>
-      <c r="L48" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="L48">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="M48">
         <v>5.24</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49">
         <v>4.22</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>5.5</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>5.83</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>6.13</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>5.37</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>5.78</v>
       </c>
-      <c r="H49" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="H49">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="I49">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J49">
         <v>5.47</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49">
         <v>5.74</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49">
         <v>4.99</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49">
         <v>5.23</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>HUN</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50">
         <v>5.87</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>5.5</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>5.93</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>4.47</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>5.41</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>3.96</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>4.47</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>5.43</v>
       </c>
-      <c r="J50" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K50" t="n">
+      <c r="J50">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K50">
         <v>6.35</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50">
         <v>4.83</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50">
         <v>5.21</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51">
         <v>5.56</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>6.01</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>6.11</v>
       </c>
-      <c r="E51" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="E51">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F51">
         <v>5.39</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>4.07</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>4.67</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>5.88</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51">
         <v>5.18</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>2.67</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51">
         <v>4.76</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51">
         <v>5.17</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>GHA</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52">
         <v>3.68</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>5.5</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>5.82</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>8.49</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>5.62</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>5.65</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>3.08</v>
       </c>
-      <c r="I52" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="I52">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J52">
         <v>5.32</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52">
         <v>1.42</v>
       </c>
-      <c r="L52" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="M52" t="n">
+      <c r="L52">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="M52">
         <v>5.15</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53">
         <v>4.41</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>5.5</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>4.68</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>5.86</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>5.08</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>5.39</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>3.61</v>
       </c>
-      <c r="I53" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="I53">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J53">
         <v>6.33</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53">
         <v>8.26</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53">
         <v>5.23</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53">
         <v>5.13</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>PHL</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54">
         <v>4.75</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>3.7</v>
       </c>
-      <c r="D54" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="D54">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="E54">
         <v>5.47</v>
       </c>
-      <c r="F54" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="F54">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="G54">
         <v>7.25</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>5.49</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>4.74</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>6.45</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>5.07</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54">
         <v>5.8</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54">
         <v>5.05</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>KEN</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55">
         <v>4.49</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>3.99</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>4.93</v>
       </c>
-      <c r="E55" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="E55">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="F55">
         <v>5.17</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>6.3</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>3.61</v>
       </c>
-      <c r="I55" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="I55">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="J55">
         <v>5.32</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>3.24</v>
       </c>
-      <c r="L55" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="M55" t="n">
+      <c r="L55">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="M55">
         <v>5.03</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56">
         <v>7.15</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>5.5</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>6</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>3.55</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>5.38</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>3.35</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>5.73</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>6.01</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>1.44</v>
       </c>
-      <c r="K56" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="L56" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="K56">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="L56">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="M56">
         <v>5.01</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>QAT</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57">
         <v>5.72</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>5.5</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>6</v>
       </c>
-      <c r="E57" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="F57" t="n">
+      <c r="E57">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="F57">
         <v>5.57</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>2.37</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>4.45</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>5.82</v>
       </c>
-      <c r="J57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K57" t="n">
+      <c r="J57">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K57">
         <v>6.94</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57">
         <v>3.96</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57">
         <v>5.01</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>LKA</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="C58" t="n">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="C58">
         <v>5.5</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>5.66</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>5.6</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>5.33</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>5.05</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>3.34</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>4.68</v>
       </c>
-      <c r="J58" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="J58">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="K58">
         <v>3.67</v>
       </c>
-      <c r="L58" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="L58">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="M58">
         <v>5</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>TUR</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59">
         <v>6.12</v>
       </c>
-      <c r="C59" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="D59" t="n">
+      <c r="C59">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="D59">
         <v>4.32</v>
       </c>
-      <c r="E59" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="F59" t="n">
+      <c r="E59">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="F59">
         <v>4.2</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>6.85</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>7</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>5.37</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>6.71</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K59">
         <v>6.42</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59">
         <v>6.44</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59">
         <v>4.99</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>MYS</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60">
         <v>5.57</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>3.99</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>5.03</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>4.74</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>4.8</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>5.69</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>5.37</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>4.91</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>5.7</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K60">
         <v>4.78</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60">
         <v>5.32</v>
       </c>
-      <c r="M60" t="n">
-        <v>4.98</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
+      <c r="M60">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61">
         <v>2.21</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>5.5</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>5.5</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>10</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>5.09</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>5.77</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>3.37</v>
       </c>
-      <c r="I61" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="I61">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J61">
         <v>5.99</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K61">
         <v>3.88</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61">
         <v>4.74</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61">
         <v>4.97</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>OMN</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="C62" t="n">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="C62">
         <v>5.5</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>5.99</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>6.75</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>5.67</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>3.18</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>3.45</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>5.22</v>
       </c>
-      <c r="J62" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="K62" t="n">
+      <c r="J62">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="K62">
         <v>3.17</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62">
         <v>3.62</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62">
         <v>4.95</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63">
         <v>4.7</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>3.87</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>4.38</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>4.66</v>
       </c>
-      <c r="F63" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="G63" t="n">
+      <c r="F63">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="G63">
         <v>6.02</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>5.95</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>4.74</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63">
         <v>7.09</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63">
         <v>6.94</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63">
         <v>5.99</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63">
         <v>4.95</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>ARE</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64">
         <v>5.44</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>5.5</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>5.94</v>
       </c>
-      <c r="E64" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="F64" t="n">
+      <c r="E64">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F64">
         <v>5.18</v>
       </c>
-      <c r="G64" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H64" t="n">
+      <c r="G64">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="H64">
         <v>5.74</v>
       </c>
-      <c r="I64" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="I64">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J64">
         <v>1.48</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K64">
         <v>7.31</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64">
         <v>4.45</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64">
         <v>4.93</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="C65" t="n">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="C65">
         <v>4.24</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>4.29</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>5.62</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>4.62</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>5.64</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>4.84</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>4.68</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65">
         <v>6.77</v>
       </c>
-      <c r="K65" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="L65" t="n">
+      <c r="K65">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="L65">
         <v>5.34</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65">
         <v>4.87</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>BGR</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66">
         <v>5.56</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>3.91</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>5.17</v>
       </c>
-      <c r="E66" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="F66" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G66" t="n">
+      <c r="E66">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="F66">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G66">
         <v>3.44</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>3.53</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>5.09</v>
       </c>
-      <c r="J66" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="K66" t="n">
+      <c r="J66">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="K66">
         <v>5.65</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66">
         <v>4.42</v>
       </c>
-      <c r="M66" t="n">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>MEX</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
+      <c r="M66">
+        <v>4.7300000000000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67">
         <v>5.07</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>2.96</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>2.21</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>5.47</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>3.67</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67">
         <v>7.41</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>7.44</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>4.7</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>6.93</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67">
         <v>6.94</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67">
         <v>6.6</v>
       </c>
-      <c r="M67" t="n">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>LTU</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
+      <c r="M67">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68">
         <v>5.56</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>5.47</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>5.54</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>3.84</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>5.05</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>2.38</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>3.13</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>5.51</v>
       </c>
-      <c r="J68" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="K68" t="n">
+      <c r="J68">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="K68">
         <v>4.43</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68">
         <v>4.03</v>
       </c>
-      <c r="M68" t="n">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>JOR</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
+      <c r="M68">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69">
         <v>3.17</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>5.5</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>5.9</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>6.95</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>5.17</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>4.21</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>2.48</v>
       </c>
-      <c r="I69" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J69" t="n">
+      <c r="I69">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J69">
         <v>2.56</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K69">
         <v>5.94</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69">
         <v>3.73</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69">
         <v>4.67</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>KWT</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70">
         <v>3.14</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>5.5</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>5.98</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>4.78</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>4.71</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>3.08</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70">
         <v>4.01</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>4.76</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70">
         <v>3.25</v>
       </c>
-      <c r="K70" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="L70" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="M70" t="n">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>DOM</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
+      <c r="K70">
+        <v>8.14</v>
+      </c>
+      <c r="L70">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="M70">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71">
         <v>3.65</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>4.57</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>4.22</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>6.16</v>
       </c>
-      <c r="F71" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G71" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="H71" t="n">
+      <c r="F71">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="G71">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="H71">
         <v>3.66</v>
       </c>
-      <c r="I71" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J71" t="n">
+      <c r="I71">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J71">
         <v>4.57</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>4.71</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71">
         <v>4.3</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71">
         <v>4.47</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>CHL</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72">
         <v>4.84</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>2.59</v>
       </c>
-      <c r="D72" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="D72">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E72">
         <v>3.91</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>3.76</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>4.92</v>
       </c>
-      <c r="H72" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="H72">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="I72">
         <v>4.8</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>6.11</v>
       </c>
-      <c r="K72" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="L72" t="n">
+      <c r="K72">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="L72">
         <v>5.08</v>
       </c>
-      <c r="M72" t="n">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
+      <c r="M72">
+        <v>4.2300000000000004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73">
         <v>5.52</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>1</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>1.73</v>
       </c>
-      <c r="E73" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F73" t="n">
+      <c r="E73">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F73">
         <v>2.61</v>
       </c>
-      <c r="G73" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="H73" t="n">
+      <c r="G73">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="H73">
         <v>7.67</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>4.95</v>
       </c>
-      <c r="J73" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K73" t="n">
+      <c r="J73">
+        <v>8.36</v>
+      </c>
+      <c r="K73">
         <v>5.45</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73">
         <v>6.98</v>
       </c>
-      <c r="M73" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>GTM</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
+      <c r="M73">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74">
         <v>3.86</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>2.67</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>1.98</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>6.29</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>3.37</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>4.82</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>3.53</v>
       </c>
-      <c r="I74" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J74" t="n">
+      <c r="I74">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J74">
         <v>5.35</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74">
         <v>4.99</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74">
         <v>4.58</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74">
         <v>3.79</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>ECU</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="C75" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="D75" t="n">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="C75">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="D75">
         <v>1.57</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>5.29</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>2.99</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>4.8</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>3.66</v>
       </c>
-      <c r="I75" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="I75">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J75">
         <v>5.71</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>2.93</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75">
         <v>4.47</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M75">
         <v>3.51</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76">
         <v>4.59</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>1</v>
       </c>
-      <c r="D76" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D76">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E76">
         <v>4.93</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>2.25</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76">
         <v>6.21</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76">
         <v>5.36</v>
       </c>
-      <c r="I76" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="I76">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J76">
         <v>6.69</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K76">
         <v>6.21</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76">
         <v>5.77</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M76">
         <v>3.48</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77">
         <v>4.46</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>1</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>1</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>6.12</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>2.29</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>6.46</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77">
         <v>5.3</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>4.75</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J77">
         <v>5.87</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77">
         <v>4.12</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77">
         <v>5.39</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M77">
         <v>3.37</v>
       </c>
     </row>
